--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run6/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run6/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9532,0.0082,0.0197,0.0092</t>
-  </si>
-  <si>
-    <t>0.0217,0.0003,0.0011,0.9920</t>
-  </si>
-  <si>
-    <t>0.8967,0.0074,0.0021,0.0788</t>
-  </si>
-  <si>
-    <t>0.0298,0.0011,0.0038,0.9866</t>
-  </si>
-  <si>
-    <t>0.9969,0.0012,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9945,0.0012,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9951,0.0011,0.0006,0.0015</t>
-  </si>
-  <si>
-    <t>0.9979,0.0003,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9933,0.0051,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9914,0.0068,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9977,0.0008,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9965,0.0009,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.5184,0.0208,0.5183,0.0099</t>
-  </si>
-  <si>
-    <t>0.0762,0.0139,0.9286,0.0043</t>
-  </si>
-  <si>
-    <t>0.1976,0.0136,0.8443,0.0011</t>
-  </si>
-  <si>
-    <t>0.2073,0.0133,0.8124,0.0073</t>
-  </si>
-  <si>
-    <t>0.6415,0.0058,0.5136,0.0015</t>
-  </si>
-  <si>
-    <t>0.0057,0.9911,0.0024,0.0012</t>
-  </si>
-  <si>
-    <t>0.0044,0.9905,0.0017,0.0035</t>
-  </si>
-  <si>
-    <t>0.0276,0.9482,0.0015,0.0253</t>
-  </si>
-  <si>
-    <t>0.0081,0.9849,0.0112,0.0018</t>
-  </si>
-  <si>
-    <t>0.0010,0.9967,0.0011,0.0022</t>
-  </si>
-  <si>
-    <t>0.6528,0.0078,0.4676,0.0074</t>
-  </si>
-  <si>
-    <t>0.6650,0.0020,0.4053,0.0071</t>
-  </si>
-  <si>
-    <t>0.0831,0.0010,0.9551,0.0005</t>
-  </si>
-  <si>
-    <t>0.0165,0.0054,0.9785,0.0004</t>
-  </si>
-  <si>
-    <t>0.0304,0.0034,0.9793,0.0006</t>
-  </si>
-  <si>
-    <t>0.0116,0.0004,0.9907,0.0002</t>
-  </si>
-  <si>
-    <t>0.0038,0.0022,0.9821,0.0279</t>
-  </si>
-  <si>
-    <t>0.8330,0.2303,0.0098,0.0035</t>
-  </si>
-  <si>
-    <t>0.1696,0.8146,0.0789,0.0168</t>
-  </si>
-  <si>
-    <t>0.0026,0.0111,0.9912,0.0068</t>
-  </si>
-  <si>
-    <t>0.0644,0.8042,0.2127,0.0014</t>
-  </si>
-  <si>
-    <t>0.9108,0.0481,0.0250,0.0222</t>
-  </si>
-  <si>
-    <t>0.7328,0.0176,0.2718,0.0056</t>
-  </si>
-  <si>
-    <t>0.9311,0.0722,0.0065,0.0014</t>
-  </si>
-  <si>
-    <t>0.0139,0.9756,0.1055,0.0036</t>
-  </si>
-  <si>
-    <t>0.3298,0.2615,0.2601,0.0161</t>
-  </si>
-  <si>
-    <t>0.1377,0.0337,0.8009,0.0285</t>
-  </si>
-  <si>
-    <t>0.0249,0.0164,0.9530,0.0035</t>
-  </si>
-  <si>
-    <t>0.0757,0.0007,0.9592,0.0005</t>
-  </si>
-  <si>
-    <t>0.0073,0.3269,0.9839,0.0030</t>
-  </si>
-  <si>
-    <t>0.0202,0.9419,0.0274,0.0026</t>
-  </si>
-  <si>
-    <t>0.0028,0.0018,0.9926,0.0032</t>
-  </si>
-  <si>
-    <t>0.2161,0.2897,0.0207,0.5716</t>
-  </si>
-  <si>
-    <t>0.0078,0.9666,0.0210,0.0182</t>
-  </si>
-  <si>
-    <t>0.0110,0.9739,0.0294,0.0010</t>
-  </si>
-  <si>
-    <t>0.0005,0.9967,0.0024,0.0024</t>
-  </si>
-  <si>
-    <t>0.0038,0.0203,0.9696,0.0263</t>
-  </si>
-  <si>
-    <t>0.0009,0.7245,0.9942,0.0011</t>
-  </si>
-  <si>
-    <t>0.0155,0.0045,0.9616,0.0082</t>
-  </si>
-  <si>
-    <t>0.0068,0.0009,0.9923,0.0021</t>
-  </si>
-  <si>
-    <t>0.0289,0.0077,0.9644,0.0037</t>
-  </si>
-  <si>
-    <t>0.0057,0.0076,0.9821,0.0019</t>
-  </si>
-  <si>
-    <t>0.9718,0.0294,0.0014,0.0029</t>
-  </si>
-  <si>
-    <t>0.9939,0.0040,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9644,0.0249,0.0054,0.0040</t>
-  </si>
-  <si>
-    <t>0.0204,0.0071,0.9795,0.0153</t>
-  </si>
-  <si>
-    <t>0.9944,0.0021,0.0007,0.0009</t>
-  </si>
-  <si>
-    <t>0.9964,0.0014,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9909,0.0034,0.0016,0.0021</t>
-  </si>
-  <si>
-    <t>0.0019,0.9436,0.9764,0.0008</t>
-  </si>
-  <si>
-    <t>0.0099,0.0775,0.9676,0.0168</t>
-  </si>
-  <si>
-    <t>0.0033,0.0018,0.9818,0.0140</t>
-  </si>
-  <si>
-    <t>0.0004,0.9875,0.9815,0.0002</t>
-  </si>
-  <si>
-    <t>0.0027,0.0016,0.9854,0.0154</t>
-  </si>
-  <si>
-    <t>0.0887,0.8972,0.0182,0.0022</t>
-  </si>
-  <si>
-    <t>0.0029,0.9937,0.0031,0.0015</t>
-  </si>
-  <si>
-    <t>0.8346,0.0056,0.2488,0.0061</t>
-  </si>
-  <si>
-    <t>0.4261,0.1015,0.5984,0.0154</t>
-  </si>
-  <si>
-    <t>0.0078,0.0135,0.9883,0.0044</t>
-  </si>
-  <si>
-    <t>0.0012,0.9706,0.9158,0.0003</t>
-  </si>
-  <si>
-    <t>0.0013,0.9559,0.8134,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9979,0.3389,0.0004</t>
-  </si>
-  <si>
-    <t>0.0104,0.9532,0.7825,0.0024</t>
-  </si>
-  <si>
-    <t>0.0134,0.0002,0.0027,0.9935</t>
-  </si>
-  <si>
-    <t>0.0015,0.0007,0.0007,0.9987</t>
-  </si>
-  <si>
-    <t>0.0017,0.0110,0.0042,0.9967</t>
-  </si>
-  <si>
-    <t>0.0042,0.0049,0.0010,0.9965</t>
-  </si>
-  <si>
-    <t>0.0040,0.0003,0.0045,0.9966</t>
-  </si>
-  <si>
-    <t>0.0037,0.0099,0.0005,0.9963</t>
-  </si>
-  <si>
-    <t>0.0080,0.8770,0.9210,0.0024</t>
-  </si>
-  <si>
-    <t>0.0017,0.9543,0.9643,0.0005</t>
-  </si>
-  <si>
-    <t>0.0026,0.9814,0.5880,0.0008</t>
-  </si>
-  <si>
-    <t>0.0029,0.9214,0.9489,0.0012</t>
-  </si>
-  <si>
-    <t>0.0008,0.9949,0.6222,0.0002</t>
-  </si>
-  <si>
-    <t>0.0245,0.8311,0.3311,0.0015</t>
-  </si>
-  <si>
-    <t>0.9942,0.0021,0.0008,0.0012</t>
-  </si>
-  <si>
-    <t>0.9823,0.0245,0.0018,0.0005</t>
-  </si>
-  <si>
-    <t>0.9865,0.0101,0.0010,0.0016</t>
-  </si>
-  <si>
-    <t>0.9936,0.0047,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9912,0.0082,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9954,0.0032,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9923,0.0012,0.0008,0.0033</t>
-  </si>
-  <si>
-    <t>0.9889,0.0065,0.0034,0.0009</t>
-  </si>
-  <si>
-    <t>0.9966,0.0013,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9976,0.0009,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9942,0.0013,0.0002,0.0018</t>
-  </si>
-  <si>
-    <t>0.9964,0.0012,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9972,0.0003,0.0000,0.0018</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.0016,0.0071,0.9946,0.0046</t>
-  </si>
-  <si>
-    <t>0.0047,0.0049,0.9875,0.0027</t>
-  </si>
-  <si>
-    <t>0.9498,0.0105,0.0177,0.0072</t>
-  </si>
-  <si>
-    <t>0.0076,0.0037,0.9763,0.0092</t>
-  </si>
-  <si>
-    <t>0.0124,0.9819,0.0021,0.0050</t>
-  </si>
-  <si>
-    <t>0.0021,0.9945,0.0015,0.0042</t>
-  </si>
-  <si>
-    <t>0.0220,0.9651,0.0113,0.0086</t>
-  </si>
-  <si>
-    <t>0.0774,0.9133,0.0072,0.0071</t>
-  </si>
-  <si>
-    <t>0.0689,0.9400,0.0032,0.0021</t>
-  </si>
-  <si>
-    <t>0.0097,0.9825,0.0021,0.0034</t>
-  </si>
-  <si>
-    <t>0.5999,0.5343,0.0098,0.0030</t>
-  </si>
-  <si>
-    <t>0.4647,0.2893,0.2594,0.0525</t>
-  </si>
-  <si>
-    <t>0.2979,0.0040,0.8226,0.0012</t>
-  </si>
-  <si>
-    <t>0.4842,0.0243,0.5788,0.0117</t>
-  </si>
-  <si>
-    <t>0.1262,0.0137,0.8645,0.0149</t>
-  </si>
-  <si>
-    <t>0.0370,0.0473,0.0456,0.9258</t>
-  </si>
-  <si>
-    <t>0.0056,0.9827,0.0242,0.0186</t>
-  </si>
-  <si>
-    <t>0.0005,0.9961,0.0030,0.0062</t>
-  </si>
-  <si>
-    <t>0.0039,0.9710,0.0041,0.1472</t>
-  </si>
-  <si>
-    <t>0.0103,0.8770,0.8697,0.0032</t>
-  </si>
-  <si>
-    <t>0.0120,0.9815,0.0350,0.0008</t>
-  </si>
-  <si>
-    <t>0.8269,0.1658,0.0411,0.0029</t>
-  </si>
-  <si>
-    <t>0.8084,0.1753,0.0351,0.0034</t>
-  </si>
-  <si>
-    <t>0.9861,0.0106,0.0011,0.0014</t>
-  </si>
-  <si>
-    <t>0.9805,0.0037,0.0078,0.0054</t>
-  </si>
-  <si>
-    <t>0.9820,0.0088,0.0028,0.0034</t>
-  </si>
-  <si>
-    <t>0.9935,0.0021,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.9978,0.0009,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9925,0.0013,0.0024,0.0010</t>
-  </si>
-  <si>
-    <t>0.9944,0.0019,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9946,0.0009,0.0007,0.0010</t>
-  </si>
-  <si>
-    <t>0.0088,0.2512,0.9628,0.0022</t>
-  </si>
-  <si>
-    <t>0.0016,0.8560,0.9640,0.0002</t>
-  </si>
-  <si>
-    <t>0.0040,0.2000,0.9619,0.0004</t>
-  </si>
-  <si>
-    <t>0.0133,0.0158,0.9778,0.0013</t>
-  </si>
-  <si>
-    <t>0.9822,0.0012,0.0147,0.0004</t>
-  </si>
-  <si>
-    <t>0.2798,0.0110,0.7831,0.0019</t>
-  </si>
-  <si>
-    <t>0.2866,0.0020,0.8554,0.0034</t>
-  </si>
-  <si>
-    <t>0.6375,0.1447,0.0599,0.1337</t>
-  </si>
-  <si>
-    <t>0.0553,0.0036,0.0026,0.9765</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.0031,0.9996</t>
-  </si>
-  <si>
-    <t>0.0015,0.0129,0.0026,0.9975</t>
-  </si>
-  <si>
-    <t>0.0023,0.0002,0.0046,0.9978</t>
-  </si>
-  <si>
-    <t>0.0012,0.9840,0.0637,0.0010</t>
-  </si>
-  <si>
-    <t>0.9876,0.0077,0.0009,0.0014</t>
-  </si>
-  <si>
-    <t>0.0769,0.9235,0.0020,0.0100</t>
-  </si>
-  <si>
-    <t>0.9865,0.0014,0.0009,0.0086</t>
-  </si>
-  <si>
-    <t>0.7581,0.4013,0.0012,0.0015</t>
-  </si>
-  <si>
-    <t>0.9859,0.0021,0.0066,0.0017</t>
-  </si>
-  <si>
-    <t>0.8186,0.0236,0.0838,0.1332</t>
-  </si>
-  <si>
-    <t>0.9832,0.0021,0.0030,0.0072</t>
-  </si>
-  <si>
-    <t>0.0372,0.0269,0.9627,0.0167</t>
-  </si>
-  <si>
-    <t>0.9395,0.0001,0.0022,0.0740</t>
-  </si>
-  <si>
-    <t>0.9779,0.0011,0.0053,0.0107</t>
-  </si>
-  <si>
-    <t>0.5958,0.2471,0.1148,0.0262</t>
-  </si>
-  <si>
-    <t>0.9674,0.0205,0.0056,0.0018</t>
-  </si>
-  <si>
-    <t>0.9223,0.0372,0.0336,0.0024</t>
-  </si>
-  <si>
-    <t>0.1555,0.4402,0.2410,0.1538</t>
-  </si>
-  <si>
-    <t>0.8802,0.0455,0.0570,0.0038</t>
-  </si>
-  <si>
-    <t>0.7031,0.1619,0.1066,0.0063</t>
-  </si>
-  <si>
-    <t>0.9884,0.0058,0.0014,0.0020</t>
-  </si>
-  <si>
-    <t>0.9891,0.0035,0.0030,0.0014</t>
-  </si>
-  <si>
-    <t>0.9924,0.0026,0.0014,0.0013</t>
-  </si>
-  <si>
-    <t>0.9873,0.0011,0.0046,0.0042</t>
-  </si>
-  <si>
-    <t>0.9902,0.0046,0.0011,0.0014</t>
-  </si>
-  <si>
-    <t>0.9859,0.0118,0.0024,0.0008</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9965,0.0007,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9418,0.0551,0.0021,0.0055</t>
-  </si>
-  <si>
-    <t>0.6133,0.5620,0.0017,0.0013</t>
-  </si>
-  <si>
-    <t>0.7752,0.3374,0.0090,0.0017</t>
-  </si>
-  <si>
-    <t>0.0541,0.1231,0.9426,0.0092</t>
-  </si>
-  <si>
-    <t>0.9767,0.0321,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.9756,0.0082,0.0077,0.0034</t>
-  </si>
-  <si>
-    <t>0.9906,0.0066,0.0008,0.0008</t>
-  </si>
-  <si>
-    <t>0.9570,0.0408,0.0026,0.0052</t>
-  </si>
-  <si>
-    <t>0.0003,0.0044,0.9986,0.0037</t>
-  </si>
-  <si>
-    <t>0.9805,0.0104,0.0037,0.0025</t>
-  </si>
-  <si>
-    <t>0.0044,0.0036,0.9912,0.0006</t>
-  </si>
-  <si>
-    <t>0.0127,0.0808,0.9540,0.0147</t>
-  </si>
-  <si>
-    <t>0.0143,0.0012,0.9898,0.0004</t>
-  </si>
-  <si>
-    <t>0.0274,0.0250,0.9708,0.0006</t>
-  </si>
-  <si>
-    <t>0.0091,0.0131,0.9842,0.0025</t>
-  </si>
-  <si>
-    <t>0.0120,0.0037,0.9882,0.0011</t>
-  </si>
-  <si>
-    <t>0.0095,0.0036,0.9846,0.0040</t>
-  </si>
-  <si>
-    <t>0.0442,0.0265,0.9342,0.0053</t>
-  </si>
-  <si>
-    <t>0.0400,0.0054,0.9615,0.0008</t>
-  </si>
-  <si>
-    <t>0.5816,0.0140,0.5555,0.0090</t>
-  </si>
-  <si>
-    <t>0.1231,0.0259,0.8534,0.0054</t>
-  </si>
-  <si>
-    <t>0.0696,0.1710,0.7724,0.0019</t>
-  </si>
-  <si>
-    <t>0.2529,0.0108,0.7442,0.0005</t>
-  </si>
-  <si>
-    <t>0.7758,0.0225,0.2148,0.0284</t>
-  </si>
-  <si>
-    <t>0.3243,0.0647,0.6376,0.0173</t>
-  </si>
-  <si>
-    <t>0.1855,0.8544,0.0056,0.0046</t>
-  </si>
-  <si>
-    <t>0.5643,0.5661,0.0128,0.0017</t>
-  </si>
-  <si>
-    <t>0.9078,0.1470,0.0013,0.0026</t>
-  </si>
-  <si>
-    <t>0.9432,0.1283,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9398,0.1003,0.0017,0.0018</t>
-  </si>
-  <si>
-    <t>0.7635,0.0337,0.2456,0.0040</t>
-  </si>
-  <si>
-    <t>0.9402,0.0004,0.1703,0.0002</t>
-  </si>
-  <si>
-    <t>0.9369,0.0095,0.0432,0.0058</t>
-  </si>
-  <si>
-    <t>0.3538,0.0023,0.6761,0.0201</t>
-  </si>
-  <si>
-    <t>0.8595,0.0098,0.1820,0.0056</t>
-  </si>
-  <si>
-    <t>0.0103,0.0029,0.9849,0.0031</t>
-  </si>
-  <si>
-    <t>0.0399,0.0139,0.9084,0.0323</t>
-  </si>
-  <si>
-    <t>0.0312,0.0192,0.9482,0.0006</t>
-  </si>
-  <si>
-    <t>0.0603,0.0094,0.9432,0.0030</t>
-  </si>
-  <si>
-    <t>0.0308,0.0421,0.9411,0.0029</t>
-  </si>
-  <si>
-    <t>0.9917,0.0032,0.0001,0.0014</t>
-  </si>
-  <si>
-    <t>0.9927,0.0026,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.9934,0.0012,0.0003,0.0032</t>
-  </si>
-  <si>
-    <t>0.9910,0.0053,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.9916,0.0026,0.0009,0.0019</t>
-  </si>
-  <si>
-    <t>0.9798,0.0061,0.0010,0.0091</t>
-  </si>
-  <si>
-    <t>0.9958,0.0007,0.0001,0.0018</t>
-  </si>
-  <si>
-    <t>0.9955,0.0011,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.0426,0.0188,0.9398,0.0207</t>
-  </si>
-  <si>
-    <t>0.1864,0.2181,0.6517,0.0110</t>
-  </si>
-  <si>
-    <t>0.8444,0.0045,0.1830,0.0060</t>
-  </si>
-  <si>
-    <t>0.0030,0.0036,0.9943,0.0007</t>
-  </si>
-  <si>
-    <t>0.0103,0.0192,0.9794,0.0113</t>
-  </si>
-  <si>
-    <t>0.0033,0.3813,0.9650,0.0020</t>
-  </si>
-  <si>
-    <t>0.0036,0.0028,0.9948,0.0013</t>
-  </si>
-  <si>
-    <t>0.0055,0.0071,0.9804,0.0102</t>
-  </si>
-  <si>
-    <t>0.0023,0.0051,0.9936,0.0024</t>
-  </si>
-  <si>
-    <t>0.0084,0.0174,0.9776,0.0061</t>
-  </si>
-  <si>
-    <t>0.0194,0.0170,0.9547,0.0204</t>
-  </si>
-  <si>
-    <t>0.7288,0.0017,0.5326,0.0009</t>
-  </si>
-  <si>
-    <t>0.2964,0.0064,0.7986,0.0119</t>
-  </si>
-  <si>
-    <t>0.9238,0.0087,0.0668,0.0037</t>
-  </si>
-  <si>
-    <t>0.9888,0.0092,0.0003,0.0012</t>
-  </si>
-  <si>
-    <t>0.9927,0.0028,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.9976,0.0019,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9933,0.0037,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.9987,0.0007,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9900,0.0096,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9962,0.0050,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9963,0.0007,0.0001,0.0016</t>
-  </si>
-  <si>
-    <t>0.0024,0.0102,0.9929,0.0004</t>
-  </si>
-  <si>
-    <t>0.0051,0.0097,0.9857,0.0052</t>
-  </si>
-  <si>
-    <t>0.0066,0.0059,0.9775,0.0060</t>
-  </si>
-  <si>
-    <t>0.0526,0.1195,0.7951,0.0078</t>
-  </si>
-  <si>
-    <t>0.0118,0.0017,0.9733,0.0064</t>
-  </si>
-  <si>
-    <t>0.3105,0.0138,0.6717,0.0483</t>
-  </si>
-  <si>
-    <t>0.2494,0.0016,0.8971,0.0008</t>
-  </si>
-  <si>
-    <t>0.0292,0.0091,0.9463,0.0122</t>
-  </si>
-  <si>
-    <t>0.9016,0.0004,0.0003,0.2532</t>
-  </si>
-  <si>
-    <t>0.0027,0.0027,0.0001,0.9982</t>
-  </si>
-  <si>
-    <t>0.0313,0.0136,0.0008,0.9835</t>
-  </si>
-  <si>
-    <t>0.0059,0.0009,0.0017,0.9965</t>
-  </si>
-  <si>
-    <t>0.0024,0.0010,0.0001,0.9985</t>
-  </si>
-  <si>
-    <t>0.6951,0.0188,0.0031,0.2870</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9671,0.0068,0.0117,0.0058</t>
+  </si>
+  <si>
+    <t>0.0147,0.0020,0.0004,0.9940</t>
+  </si>
+  <si>
+    <t>0.9633,0.0024,0.0011,0.0306</t>
+  </si>
+  <si>
+    <t>0.0408,0.0008,0.0020,0.9861</t>
+  </si>
+  <si>
+    <t>0.9956,0.0014,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9948,0.0017,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9976,0.0011,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9965,0.0004,0.0005,0.0018</t>
+  </si>
+  <si>
+    <t>0.9958,0.0022,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9971,0.0010,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9966,0.0017,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9968,0.0003,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.8342,0.0187,0.1964,0.0055</t>
+  </si>
+  <si>
+    <t>0.1027,0.0106,0.9208,0.0033</t>
+  </si>
+  <si>
+    <t>0.0384,0.0040,0.9724,0.0003</t>
+  </si>
+  <si>
+    <t>0.0394,0.0037,0.9511,0.0072</t>
+  </si>
+  <si>
+    <t>0.9120,0.0028,0.1351,0.0014</t>
+  </si>
+  <si>
+    <t>0.0016,0.9955,0.0063,0.0008</t>
+  </si>
+  <si>
+    <t>0.0024,0.9935,0.0047,0.0014</t>
+  </si>
+  <si>
+    <t>0.0366,0.9464,0.0016,0.0093</t>
+  </si>
+  <si>
+    <t>0.0152,0.9741,0.0084,0.0025</t>
+  </si>
+  <si>
+    <t>0.0008,0.9969,0.0022,0.0010</t>
+  </si>
+  <si>
+    <t>0.4340,0.0417,0.3521,0.1617</t>
+  </si>
+  <si>
+    <t>0.3880,0.0020,0.7342,0.0034</t>
+  </si>
+  <si>
+    <t>0.0111,0.0015,0.9875,0.0003</t>
+  </si>
+  <si>
+    <t>0.0780,0.0071,0.9314,0.0028</t>
+  </si>
+  <si>
+    <t>0.0447,0.0063,0.9667,0.0006</t>
+  </si>
+  <si>
+    <t>0.0225,0.0016,0.9734,0.0014</t>
+  </si>
+  <si>
+    <t>0.0015,0.0027,0.9830,0.0819</t>
+  </si>
+  <si>
+    <t>0.6818,0.4461,0.0037,0.0033</t>
+  </si>
+  <si>
+    <t>0.1649,0.3097,0.7400,0.0129</t>
+  </si>
+  <si>
+    <t>0.0105,0.0062,0.9745,0.0207</t>
+  </si>
+  <si>
+    <t>0.0269,0.8219,0.1789,0.0019</t>
+  </si>
+  <si>
+    <t>0.8643,0.0911,0.0180,0.0252</t>
+  </si>
+  <si>
+    <t>0.9161,0.0147,0.0741,0.0029</t>
+  </si>
+  <si>
+    <t>0.8125,0.1816,0.0209,0.0040</t>
+  </si>
+  <si>
+    <t>0.0103,0.9790,0.0577,0.0034</t>
+  </si>
+  <si>
+    <t>0.2006,0.1521,0.5988,0.0265</t>
+  </si>
+  <si>
+    <t>0.1471,0.1598,0.6923,0.0365</t>
+  </si>
+  <si>
+    <t>0.0069,0.1438,0.9621,0.0041</t>
+  </si>
+  <si>
+    <t>0.0242,0.0027,0.9447,0.0289</t>
+  </si>
+  <si>
+    <t>0.0131,0.2178,0.9753,0.0054</t>
+  </si>
+  <si>
+    <t>0.0085,0.9720,0.0451,0.0012</t>
+  </si>
+  <si>
+    <t>0.0192,0.0023,0.9789,0.0031</t>
+  </si>
+  <si>
+    <t>0.1016,0.4392,0.1161,0.7080</t>
+  </si>
+  <si>
+    <t>0.0111,0.9675,0.0401,0.0120</t>
+  </si>
+  <si>
+    <t>0.0071,0.9735,0.1058,0.0040</t>
+  </si>
+  <si>
+    <t>0.0014,0.9946,0.0112,0.0013</t>
+  </si>
+  <si>
+    <t>0.0144,0.0324,0.9694,0.0082</t>
+  </si>
+  <si>
+    <t>0.0057,0.6587,0.9858,0.0015</t>
+  </si>
+  <si>
+    <t>0.0143,0.0010,0.9891,0.0001</t>
+  </si>
+  <si>
+    <t>0.0111,0.0009,0.9656,0.0552</t>
+  </si>
+  <si>
+    <t>0.0075,0.0098,0.9872,0.0014</t>
+  </si>
+  <si>
+    <t>0.0038,0.0023,0.9918,0.0033</t>
+  </si>
+  <si>
+    <t>0.9612,0.0716,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.9867,0.0044,0.0038,0.0017</t>
+  </si>
+  <si>
+    <t>0.9760,0.0050,0.0078,0.0056</t>
+  </si>
+  <si>
+    <t>0.0058,0.0160,0.9901,0.0141</t>
+  </si>
+  <si>
+    <t>0.9961,0.0005,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9966,0.0018,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9800,0.0223,0.0029,0.0008</t>
+  </si>
+  <si>
+    <t>0.0045,0.9273,0.9396,0.0012</t>
+  </si>
+  <si>
+    <t>0.0040,0.1144,0.9762,0.0101</t>
+  </si>
+  <si>
+    <t>0.0087,0.0497,0.9502,0.0230</t>
+  </si>
+  <si>
+    <t>0.0050,0.9092,0.9421,0.0041</t>
+  </si>
+  <si>
+    <t>0.0044,0.0007,0.9964,0.0003</t>
+  </si>
+  <si>
+    <t>0.0174,0.9728,0.0096,0.0014</t>
+  </si>
+  <si>
+    <t>0.0105,0.9861,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.7827,0.0074,0.4217,0.0022</t>
+  </si>
+  <si>
+    <t>0.7728,0.0397,0.2074,0.0247</t>
+  </si>
+  <si>
+    <t>0.0403,0.0237,0.9515,0.0088</t>
+  </si>
+  <si>
+    <t>0.0065,0.9182,0.7919,0.0015</t>
+  </si>
+  <si>
+    <t>0.0013,0.8886,0.8302,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9974,0.1564,0.0002</t>
+  </si>
+  <si>
+    <t>0.0104,0.9569,0.3996,0.0041</t>
+  </si>
+  <si>
+    <t>0.0138,0.0003,0.0009,0.9946</t>
+  </si>
+  <si>
+    <t>0.0083,0.0031,0.0006,0.9956</t>
+  </si>
+  <si>
+    <t>0.0019,0.0033,0.0004,0.9983</t>
+  </si>
+  <si>
+    <t>0.0076,0.0029,0.0027,0.9935</t>
+  </si>
+  <si>
+    <t>0.0329,0.0013,0.0072,0.9820</t>
+  </si>
+  <si>
+    <t>0.0028,0.0098,0.0034,0.9964</t>
+  </si>
+  <si>
+    <t>0.0164,0.9337,0.5573,0.0082</t>
+  </si>
+  <si>
+    <t>0.0122,0.6969,0.9538,0.0031</t>
+  </si>
+  <si>
+    <t>0.0013,0.9823,0.7407,0.0015</t>
+  </si>
+  <si>
+    <t>0.0022,0.6418,0.9762,0.0008</t>
+  </si>
+  <si>
+    <t>0.0003,0.9968,0.1899,0.0000</t>
+  </si>
+  <si>
+    <t>0.0118,0.6996,0.7190,0.0096</t>
+  </si>
+  <si>
+    <t>0.9978,0.0008,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9958,0.0026,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9891,0.0072,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9945,0.0041,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9927,0.0048,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9953,0.0030,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9948,0.0015,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.9910,0.0047,0.0023,0.0008</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9858,0.0169,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9960,0.0021,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.0049,0.9951,0.0033</t>
+  </si>
+  <si>
+    <t>0.0094,0.0112,0.9837,0.0034</t>
+  </si>
+  <si>
+    <t>0.9594,0.0074,0.0209,0.0016</t>
+  </si>
+  <si>
+    <t>0.0015,0.0003,0.9944,0.0039</t>
+  </si>
+  <si>
+    <t>0.0132,0.9761,0.0012,0.0070</t>
+  </si>
+  <si>
+    <t>0.0046,0.9902,0.0052,0.0037</t>
+  </si>
+  <si>
+    <t>0.1699,0.8469,0.0059,0.0075</t>
+  </si>
+  <si>
+    <t>0.0911,0.9127,0.0134,0.0074</t>
+  </si>
+  <si>
+    <t>0.0367,0.9602,0.0036,0.0065</t>
+  </si>
+  <si>
+    <t>0.0013,0.9964,0.0002,0.0024</t>
+  </si>
+  <si>
+    <t>0.7401,0.3665,0.0048,0.0021</t>
+  </si>
+  <si>
+    <t>0.6306,0.0151,0.4998,0.0056</t>
+  </si>
+  <si>
+    <t>0.1803,0.0088,0.8541,0.0112</t>
+  </si>
+  <si>
+    <t>0.6097,0.0835,0.2630,0.0096</t>
+  </si>
+  <si>
+    <t>0.7212,0.0183,0.3370,0.0034</t>
+  </si>
+  <si>
+    <t>0.0092,0.0214,0.0144,0.9849</t>
+  </si>
+  <si>
+    <t>0.0044,0.9872,0.0075,0.0061</t>
+  </si>
+  <si>
+    <t>0.0008,0.9952,0.0015,0.0064</t>
+  </si>
+  <si>
+    <t>0.0121,0.9416,0.0095,0.1125</t>
+  </si>
+  <si>
+    <t>0.0041,0.8921,0.9437,0.0014</t>
+  </si>
+  <si>
+    <t>0.0034,0.9929,0.0079,0.0003</t>
+  </si>
+  <si>
+    <t>0.6747,0.3449,0.0309,0.0039</t>
+  </si>
+  <si>
+    <t>0.8100,0.2701,0.0060,0.0017</t>
+  </si>
+  <si>
+    <t>0.9892,0.0045,0.0015,0.0015</t>
+  </si>
+  <si>
+    <t>0.9920,0.0020,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.9917,0.0027,0.0007,0.0015</t>
+  </si>
+  <si>
+    <t>0.9925,0.0018,0.0015,0.0017</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9938,0.0012,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.9892,0.0009,0.0005,0.0073</t>
+  </si>
+  <si>
+    <t>0.9941,0.0008,0.0006,0.0020</t>
+  </si>
+  <si>
+    <t>0.0038,0.6177,0.9660,0.0011</t>
+  </si>
+  <si>
+    <t>0.0103,0.0532,0.9793,0.0002</t>
+  </si>
+  <si>
+    <t>0.0087,0.0104,0.9876,0.0002</t>
+  </si>
+  <si>
+    <t>0.0076,0.0064,0.9915,0.0001</t>
+  </si>
+  <si>
+    <t>0.9630,0.0129,0.0065,0.0048</t>
+  </si>
+  <si>
+    <t>0.8969,0.0090,0.1436,0.0028</t>
+  </si>
+  <si>
+    <t>0.0927,0.0037,0.9233,0.0107</t>
+  </si>
+  <si>
+    <t>0.7454,0.0466,0.2276,0.0173</t>
+  </si>
+  <si>
+    <t>0.1993,0.0019,0.0005,0.9290</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0019,0.9998</t>
+  </si>
+  <si>
+    <t>0.0011,0.0091,0.0019,0.9981</t>
+  </si>
+  <si>
+    <t>0.0039,0.0002,0.0018,0.9978</t>
+  </si>
+  <si>
+    <t>0.0037,0.9665,0.3174,0.0019</t>
+  </si>
+  <si>
+    <t>0.9902,0.0082,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.2140,0.8394,0.0043,0.0051</t>
+  </si>
+  <si>
+    <t>0.9878,0.0056,0.0018,0.0014</t>
+  </si>
+  <si>
+    <t>0.8391,0.1716,0.0061,0.0069</t>
+  </si>
+  <si>
+    <t>0.9880,0.0025,0.0027,0.0017</t>
+  </si>
+  <si>
+    <t>0.7164,0.0059,0.0138,0.4353</t>
+  </si>
+  <si>
+    <t>0.9876,0.0027,0.0031,0.0029</t>
+  </si>
+  <si>
+    <t>0.0239,0.0347,0.9698,0.0245</t>
+  </si>
+  <si>
+    <t>0.8504,0.0004,0.0068,0.1913</t>
+  </si>
+  <si>
+    <t>0.9436,0.0011,0.0249,0.0119</t>
+  </si>
+  <si>
+    <t>0.6697,0.1707,0.1446,0.0432</t>
+  </si>
+  <si>
+    <t>0.9424,0.0256,0.0206,0.0018</t>
+  </si>
+  <si>
+    <t>0.9664,0.0113,0.0170,0.0014</t>
+  </si>
+  <si>
+    <t>0.6264,0.0800,0.2813,0.0548</t>
+  </si>
+  <si>
+    <t>0.6068,0.0888,0.2498,0.0113</t>
+  </si>
+  <si>
+    <t>0.9267,0.0504,0.0153,0.0047</t>
+  </si>
+  <si>
+    <t>0.9870,0.0060,0.0013,0.0020</t>
+  </si>
+  <si>
+    <t>0.9946,0.0020,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9927,0.0012,0.0010,0.0021</t>
+  </si>
+  <si>
+    <t>0.9906,0.0007,0.0044,0.0017</t>
+  </si>
+  <si>
+    <t>0.9900,0.0017,0.0007,0.0064</t>
+  </si>
+  <si>
+    <t>0.9891,0.0096,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.9965,0.0010,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9972,0.0009,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.8607,0.1521,0.0019,0.0062</t>
+  </si>
+  <si>
+    <t>0.3131,0.7670,0.0053,0.0044</t>
+  </si>
+  <si>
+    <t>0.8688,0.1745,0.0062,0.0036</t>
+  </si>
+  <si>
+    <t>0.8244,0.1224,0.0400,0.0267</t>
+  </si>
+  <si>
+    <t>0.9592,0.0790,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9609,0.0200,0.0153,0.0048</t>
+  </si>
+  <si>
+    <t>0.9939,0.0044,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9515,0.0479,0.0021,0.0034</t>
+  </si>
+  <si>
+    <t>0.0008,0.0072,0.9977,0.0058</t>
+  </si>
+  <si>
+    <t>0.9298,0.0247,0.0485,0.0035</t>
+  </si>
+  <si>
+    <t>0.0034,0.0029,0.9948,0.0004</t>
+  </si>
+  <si>
+    <t>0.0061,0.0136,0.9929,0.0004</t>
+  </si>
+  <si>
+    <t>0.0016,0.0017,0.9950,0.0010</t>
+  </si>
+  <si>
+    <t>0.0102,0.0320,0.9844,0.0006</t>
+  </si>
+  <si>
+    <t>0.0116,0.0059,0.9833,0.0022</t>
+  </si>
+  <si>
+    <t>0.0045,0.0004,0.9952,0.0008</t>
+  </si>
+  <si>
+    <t>0.0070,0.0018,0.9912,0.0014</t>
+  </si>
+  <si>
+    <t>0.3795,0.0043,0.8027,0.0013</t>
+  </si>
+  <si>
+    <t>0.0922,0.0057,0.9382,0.0019</t>
+  </si>
+  <si>
+    <t>0.1709,0.0327,0.8209,0.0024</t>
+  </si>
+  <si>
+    <t>0.0720,0.0515,0.8834,0.0090</t>
+  </si>
+  <si>
+    <t>0.0903,0.1791,0.7030,0.0040</t>
+  </si>
+  <si>
+    <t>0.2377,0.0139,0.7440,0.0007</t>
+  </si>
+  <si>
+    <t>0.5067,0.1978,0.3621,0.0586</t>
+  </si>
+  <si>
+    <t>0.1543,0.0052,0.9020,0.0010</t>
+  </si>
+  <si>
+    <t>0.0616,0.9253,0.0210,0.0026</t>
+  </si>
+  <si>
+    <t>0.3404,0.7481,0.0072,0.0036</t>
+  </si>
+  <si>
+    <t>0.8835,0.2481,0.0024,0.0010</t>
+  </si>
+  <si>
+    <t>0.9880,0.0182,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.2718,0.8704,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.5248,0.4278,0.0173,0.0138</t>
+  </si>
+  <si>
+    <t>0.7571,0.0049,0.4159,0.0036</t>
+  </si>
+  <si>
+    <t>0.9469,0.0034,0.0512,0.0033</t>
+  </si>
+  <si>
+    <t>0.5315,0.0012,0.6995,0.0015</t>
+  </si>
+  <si>
+    <t>0.6974,0.0062,0.4758,0.0038</t>
+  </si>
+  <si>
+    <t>0.0118,0.0032,0.9817,0.0061</t>
+  </si>
+  <si>
+    <t>0.0419,0.2100,0.7683,0.0136</t>
+  </si>
+  <si>
+    <t>0.0426,0.0371,0.9574,0.0024</t>
+  </si>
+  <si>
+    <t>0.1008,0.0027,0.9307,0.0008</t>
+  </si>
+  <si>
+    <t>0.0147,0.0097,0.9858,0.0005</t>
+  </si>
+  <si>
+    <t>0.9957,0.0010,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9890,0.0119,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9931,0.0018,0.0009,0.0015</t>
+  </si>
+  <si>
+    <t>0.9952,0.0021,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9911,0.0051,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9924,0.0036,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.9911,0.0037,0.0008,0.0017</t>
+  </si>
+  <si>
+    <t>0.9934,0.0017,0.0014,0.0016</t>
+  </si>
+  <si>
+    <t>0.0668,0.0116,0.9572,0.0030</t>
+  </si>
+  <si>
+    <t>0.3490,0.0770,0.6227,0.0112</t>
+  </si>
+  <si>
+    <t>0.9314,0.0133,0.0428,0.0063</t>
+  </si>
+  <si>
+    <t>0.0094,0.0097,0.9903,0.0012</t>
+  </si>
+  <si>
+    <t>0.0005,0.0042,0.9947,0.0060</t>
+  </si>
+  <si>
+    <t>0.0079,0.2004,0.9389,0.0020</t>
+  </si>
+  <si>
+    <t>0.0045,0.0071,0.9925,0.0031</t>
+  </si>
+  <si>
+    <t>0.0058,0.0053,0.9783,0.0128</t>
+  </si>
+  <si>
+    <t>0.0057,0.0301,0.9827,0.0083</t>
+  </si>
+  <si>
+    <t>0.0038,0.0030,0.9902,0.0014</t>
+  </si>
+  <si>
+    <t>0.0306,0.0753,0.8724,0.0119</t>
+  </si>
+  <si>
+    <t>0.6070,0.0008,0.6528,0.0012</t>
+  </si>
+  <si>
+    <t>0.7792,0.0017,0.3868,0.0028</t>
+  </si>
+  <si>
+    <t>0.9706,0.0035,0.0186,0.0016</t>
+  </si>
+  <si>
+    <t>0.9918,0.0078,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9956,0.0031,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9960,0.0018,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9937,0.0020,0.0007,0.0014</t>
+  </si>
+  <si>
+    <t>0.9970,0.0010,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9925,0.0061,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9870,0.0119,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9964,0.0007,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.0085,0.0187,0.9716,0.0006</t>
+  </si>
+  <si>
+    <t>0.0038,0.0169,0.9919,0.0006</t>
+  </si>
+  <si>
+    <t>0.0056,0.0209,0.9604,0.0116</t>
+  </si>
+  <si>
+    <t>0.0058,0.0513,0.9637,0.0049</t>
+  </si>
+  <si>
+    <t>0.0084,0.0042,0.9848,0.0041</t>
+  </si>
+  <si>
+    <t>0.0855,0.0166,0.8589,0.0724</t>
+  </si>
+  <si>
+    <t>0.1065,0.0048,0.9220,0.0039</t>
+  </si>
+  <si>
+    <t>0.0106,0.0086,0.9612,0.0248</t>
+  </si>
+  <si>
+    <t>0.9128,0.0019,0.0009,0.1459</t>
+  </si>
+  <si>
+    <t>0.0050,0.0452,0.0004,0.9937</t>
+  </si>
+  <si>
+    <t>0.0332,0.0108,0.0014,0.9845</t>
+  </si>
+  <si>
+    <t>0.0020,0.0003,0.0005,0.9989</t>
+  </si>
+  <si>
+    <t>0.0011,0.0004,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.8037,0.0111,0.0086,0.2885</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1973,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2001,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2124,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2141,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2155,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2169,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2180,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2264,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2295,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2323,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2337,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2365,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2376,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2407,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2449,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2491,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2505,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2519,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2533,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2575,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2659,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2701,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2813,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2855,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2939,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2953,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2967,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3009,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3023,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3037,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3051,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3065,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3079,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3093,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3107,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3121,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3135,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3146,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>275</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3443,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3538,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3569,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3580,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3611,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3653,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3667,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3681,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3863,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3877,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3902,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3919,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3947,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3961,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3975,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3989,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4003,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4031,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4115,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4367,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4381,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4392,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4591,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4605,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4619,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4633,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4647,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4661,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4689,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4703,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4717,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4756,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4812,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4843,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4857,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4871,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4885,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4899,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5039,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5095,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5123,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5151,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5165,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5176,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5190,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5361,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5375,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5389,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5403,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5417,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5431,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5459,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5473,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5487,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5501,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
